--- a/output/full_scan/batch_seq1_2026-08-12.xlsx
+++ b/output/full_scan/batch_seq1_2026-08-12.xlsx
@@ -5467,7 +5467,7 @@
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>218.6852858415998</v>
+        <v>218.6852858415997</v>
       </c>
       <c r="E95" s="2" t="n">
         <v>28.5</v>
